--- a/data/output/evaluasi_13.xlsx
+++ b/data/output/evaluasi_13.xlsx
@@ -8,17 +8,23 @@
   </bookViews>
   <sheets>
     <sheet name="1300" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1312" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="1302" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="1303" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="1304" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="1305" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="1371" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="1372" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="1377" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="1375" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="1301" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="1311" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="1305" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="1306" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="1307" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="1311" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="1302" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="1304" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="1310" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="1312" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="1301" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="1303" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="1309" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="1374" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="1373" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="1371" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="1376" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="1372" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="1377" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,20 +488,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.119723610772427</v>
+        <v>5.132526771977278</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25</t>
+          <t>adhb_net_ekspor_q2-25</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -510,20 +516,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10.01459865658886</v>
+        <v>3.13334396535129</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q2-25</t>
+          <t>y-on-y_pdrb_q3-25 vs y-on-y_pdrb_q3-25.1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,01 point)</t>
         </is>
       </c>
     </row>
@@ -538,20 +544,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.5016383958256024</v>
+        <v>-1.185282859877784</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>q-to-q_pdrb_q1-25 vs q-to-q_pdrb_q1-25.1</t>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
         </is>
       </c>
     </row>
@@ -566,20 +572,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.5501169121095402</v>
+        <v>-1.732370638677617</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25 vs implisit_q-to-q_pkp_q1-25.1</t>
+          <t>y-on-y_pmtb_q3-25 vs y-on-y_pmtb_q3-25.1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
         </is>
       </c>
     </row>
@@ -594,20 +600,48 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9960536909233387</v>
+        <v>-0.3109308127226933</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkp_q1-25 vs implisit_y-on-y_pkp_q1-25.1</t>
+          <t>c-to-c_pkp_q2-25 vs c-to-c_pkp_q2-25.1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sumatera Barat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.6161669175984621</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25 vs c-to-c_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
         </is>
       </c>
     </row>
@@ -659,85 +693,85 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1375</v>
+        <v>1301</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Bukittinggi</t>
+          <t>Kabupaten Kepulauan Mentawai</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.1238188888050504</v>
+        <v>-3.798857293554069</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1375</v>
+        <v>1301</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kota Bukittinggi</t>
+          <t>Kabupaten Kepulauan Mentawai</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1238188888050504</v>
+        <v>0.1334593186701925</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1375</v>
+        <v>1301</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kota Bukittinggi</t>
+          <t>Kabupaten Kepulauan Mentawai</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.03082333398077439</v>
+        <v>5.444574771880174</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -752,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,29 +823,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Kepulauan Mentawai</t>
+          <t>Kabupaten Solok</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.05819317870796177</v>
+        <v>2.529450452360892</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1303</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Solok</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4.912296085626582</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -826,6 +888,600 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1309</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Pasaman</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1.585307707420015</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1309</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Pasaman</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3.322811310381932</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1374</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Padang Panjang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.108423071455814</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1374</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Padang Panjang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.738237493707434</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1374</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Padang Panjang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.8910669312262263</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1373</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Sawahlunto</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.09081115148597656</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q3-25_prov vs y-on-y_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1373</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Sawahlunto</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1116421210484218</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1371</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Padang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-4.71187695958099</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1371</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Padang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.401870694260347</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1371</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Padang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7995820749894667</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1376</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Payakumbuh</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.06525496449298653</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1376</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Payakumbuh</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.06461859781671281</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1376</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Payakumbuh</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.3131033349337113</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -863,29 +1519,159 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1311</v>
+        <v>1372</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Dharmasraya</t>
+          <t>Kota Solok</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.2811499078637541</v>
+        <v>-0.5169789111220227</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Pariaman</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.07585967669743031</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Pariaman</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.143513715252063</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Pariaman</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.257118572356327</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -900,7 +1686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -937,169 +1723,29 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1312</v>
+        <v>1305</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Pasaman Barat</t>
+          <t>Kabupaten Tanah Datar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.02170294434695832</v>
+        <v>0.693881298405197</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pklnprt_q1-25_ril vs y-on-y_pklnprt_q1-25_rev</t>
+          <t>c-to-c_pkp_q2-25_ril vs c-to-c_pkp_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1312</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Kabupaten Pasaman Barat</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>0.02170294434695832</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>c-to-c_pklnprt_q1-25_ril vs c-to-c_pklnprt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1312</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Kabupaten Pasaman Barat</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1.044955039815056</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1312</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Kabupaten Pasaman Barat</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0.2177629885891585</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1312</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kabupaten Pasaman Barat</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>1.107142146164489</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>implisit_y-on-y_pklnprt_q1-25_ril vs implisit_y-on-y_pklnprt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1312</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Kabupaten Pasaman Barat</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.0002864940491438349</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pklnprt_q1-25_ril vs sog_y-on-y_pklnprt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
@@ -1151,11 +1797,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Pesisir Selatan</t>
+          <t>Kabupaten Padang Pariaman</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1164,72 +1810,72 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.16960930487178</v>
+        <v>2.004656496476791</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Pesisir Selatan</t>
+          <t>Kabupaten Padang Pariaman</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.16960930487178</v>
+        <v>-5.413200631827216</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Pesisir Selatan</t>
+          <t>Kabupaten Padang Pariaman</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.2957353910084398</v>
+        <v>-0.7356825898349668</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1281,11 +1927,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Solok</t>
+          <t>Kabupaten Agam</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1294,72 +1940,72 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.222722837767943</v>
+        <v>2.557369710698732</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Solok</t>
+          <t>Kabupaten Agam</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.222722837767943</v>
+        <v>0.2202514591129074</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Solok</t>
+          <t>Kabupaten Agam</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.2729728486875684</v>
+        <v>-4.055275862775994</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1374,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1411,11 +2057,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1304</v>
+        <v>1311</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Sijunjung</t>
+          <t>Kabupaten Dharmasraya</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1424,72 +2070,128 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6.970306006686728</v>
+        <v>2.315780229932152</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1304</v>
+        <v>1311</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Sijunjung</t>
+          <t>Kabupaten Dharmasraya</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6.970306006686728</v>
+        <v>2.452363630144581</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1304</v>
+        <v>1311</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Sijunjung</t>
+          <t>Kabupaten Dharmasraya</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.401307261862566</v>
+        <v>1.052155501711487</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1311</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Dharmasraya</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.4817590740042231</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1311</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Dharmasraya</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8370968116486814</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1541,85 +2243,85 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1305</v>
+        <v>1302</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Tanah Datar</t>
+          <t>Kabupaten Pesisir Selatan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.349352229710259</v>
+        <v>0.6282951350957967</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1305</v>
+        <v>1302</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Tanah Datar</t>
+          <t>Kabupaten Pesisir Selatan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5.349352229710259</v>
+        <v>-0.8189687597358716</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1305</v>
+        <v>1302</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Tanah Datar</t>
+          <t>Kabupaten Pesisir Selatan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.3701552287181748</v>
+        <v>-0.2447916635490057</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1634,7 +2336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1671,85 +2373,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1371</v>
+        <v>1304</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Padang</t>
+          <t>Kabupaten Sijunjung</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.505621067910239</v>
+        <v>0.9182258466740065</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1371</v>
+        <v>1304</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kota Padang</t>
+          <t>Kabupaten Sijunjung</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.505621067910239</v>
+        <v>-1.212709680292221</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1371</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Kota Padang</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0.2974492312620554</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1764,7 +2438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1801,113 +2475,29 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1372</v>
+        <v>1310</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Solok</t>
+          <t>Kabupaten Solok Selatan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.041641554734444</v>
+        <v>0.9863527351940818</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1372</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Kota Solok</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>4.041641554734444</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1372</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Kota Solok</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0.2398531266567291</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1372</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Kota Solok</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0.4029378687783977</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1922,7 +2512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1959,169 +2549,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1377</v>
+        <v>1312</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Pariaman</t>
+          <t>Kabupaten Pasaman Barat</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7.871976970418341</v>
+        <v>2.887068295156217</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1377</v>
+        <v>1312</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kota Pariaman</t>
+          <t>Kabupaten Pasaman Barat</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1374364786334903</v>
+        <v>-0.6814073080815672</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1377</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Kota Pariaman</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>7.871976970418341</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1377</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Kota Pariaman</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0.1374364786334903</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1377</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kota Pariaman</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.5907992088340084</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1377</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Kota Pariaman</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.03369691176423281</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_13.xlsx
+++ b/data/output/evaluasi_13.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
